--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484270_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484270_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. SALAVEDRA VILARNAU</t>
+          <t>J. CALLAVE FERRER</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3444</v>
+        <v>0.1483</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5959</v>
+        <v>-0.3779</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2516</v>
+        <v>0.5261</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.0668</v>
+        <v>-1.6253</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.7427</v>
+        <v>0.5863</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3241</v>
+        <v>-2.2116</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4314</v>
+        <v>-0.8759</v>
       </c>
       <c r="K2" t="n">
-        <v>0.3505</v>
+        <v>1.0655</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0809</v>
+        <v>-1.9414</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.4982</v>
+        <v>-0.7494</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.0931</v>
+        <v>-0.4792</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.4051</v>
+        <v>-0.2702</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>0.1953</v>
       </c>
       <c r="Q2" t="n">
         <v>-1.1721</v>
       </c>
       <c r="R2" t="n">
-        <v>1.1721</v>
+        <v>1.3674</v>
       </c>
       <c r="S2" t="n">
-        <v>1.4995</v>
+        <v>0.78</v>
       </c>
       <c r="T2" t="n">
-        <v>1.0594</v>
+        <v>0.5063</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4401</v>
+        <v>0.2737</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.08840000000000001</v>
+        <v>0.7982</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2772</v>
+        <v>1.1638</v>
       </c>
       <c r="X2" t="n">
         <v>-0.3656</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. CALLAVE FERRER</t>
+          <t>J. SALAVEDRA VILARNAU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0605</v>
+        <v>-0.2369</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.4384</v>
+        <v>0.1509</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4989</v>
+        <v>-0.3877</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.6253</v>
+        <v>-1.0668</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5863</v>
+        <v>-0.7427</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.2116</v>
+        <v>-0.3241</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.8759</v>
+        <v>0.4314</v>
       </c>
       <c r="K3" t="n">
-        <v>1.0655</v>
+        <v>0.3505</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.9414</v>
+        <v>0.0809</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.7494</v>
+        <v>-1.4982</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4792</v>
+        <v>-1.0931</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2702</v>
+        <v>-0.4051</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>-1.1721</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3674</v>
+        <v>1.1721</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6923</v>
+        <v>0.9183</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4458</v>
+        <v>0.6143</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2465</v>
+        <v>0.304</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7982</v>
+        <v>-0.08840000000000001</v>
       </c>
       <c r="W3" t="n">
-        <v>1.1638</v>
+        <v>0.2772</v>
       </c>
       <c r="X3" t="n">
         <v>-0.3656</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.6762</v>
+        <v>-0.2384</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2193</v>
+        <v>1.6843</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.8955</v>
+        <v>-1.9227</v>
       </c>
       <c r="G4" t="n">
         <v>0.373</v>
@@ -766,13 +766,13 @@
         <v>2.1488</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0094</v>
+        <v>0.4471</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0359</v>
+        <v>0.5009</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0265</v>
+        <v>-0.0537</v>
       </c>
       <c r="V4" t="n">
         <v>-0.2772</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. CANO CANO</t>
+          <t>R. GUARDIOLA DISPES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.6858</v>
+        <v>-0.7095</v>
       </c>
       <c r="E5" t="n">
-        <v>2.834</v>
+        <v>2.315</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.5198</v>
+        <v>-3.0245</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0163</v>
+        <v>0.8616</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.3756</v>
+        <v>2.7086</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3918</v>
+        <v>-1.847</v>
       </c>
       <c r="J5" t="n">
-        <v>3.6124</v>
+        <v>4.5325</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6574</v>
+        <v>3.9512</v>
       </c>
       <c r="L5" t="n">
-        <v>2.955</v>
+        <v>0.5813</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.5962</v>
+        <v>-3.6708</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.033</v>
+        <v>-1.2425</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.5632</v>
+        <v>-2.4283</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.3907</v>
+        <v>0.1953</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.1488</v>
+        <v>-3.1255</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7581</v>
+        <v>3.3208</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2729</v>
+        <v>0.095</v>
       </c>
       <c r="T5" t="n">
-        <v>1.3703</v>
+        <v>0.2987</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0975</v>
+        <v>-0.2037</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.5842</v>
+        <v>-1.8615</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.6093</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.5842</v>
+        <v>-2.4708</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. GUARDIOLA DISPES</t>
+          <t>A. CANO CANO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.9507</v>
+        <v>-1.5486</v>
       </c>
       <c r="E6" t="n">
-        <v>1.1828</v>
+        <v>1.9439</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.1334</v>
+        <v>-3.4925</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8616</v>
+        <v>0.0163</v>
       </c>
       <c r="H6" t="n">
-        <v>2.7086</v>
+        <v>-0.3756</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.847</v>
+        <v>0.3918</v>
       </c>
       <c r="J6" t="n">
-        <v>4.5325</v>
+        <v>3.6124</v>
       </c>
       <c r="K6" t="n">
-        <v>3.9512</v>
+        <v>0.6574</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5813</v>
+        <v>2.955</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.6708</v>
+        <v>-3.5962</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.2425</v>
+        <v>-1.033</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.4283</v>
+        <v>-2.5632</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1953</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.1255</v>
+        <v>-2.1488</v>
       </c>
       <c r="R6" t="n">
-        <v>3.3208</v>
+        <v>1.7581</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.1462</v>
+        <v>0.41</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8335</v>
+        <v>0.4802</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3126</v>
+        <v>-0.0702</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.8615</v>
+        <v>-1.5842</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.4708</v>
+        <v>-1.5842</v>
       </c>
     </row>
     <row r="7">
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.3832</v>
+        <v>-2.8283</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3686</v>
+        <v>-0.0765</v>
       </c>
       <c r="F7" t="n">
         <v>-2.7518</v>
@@ -1000,10 +1000,10 @@
         <v>1.9534</v>
       </c>
       <c r="S7" t="n">
-        <v>1.5106</v>
+        <v>1.0655</v>
       </c>
       <c r="T7" t="n">
-        <v>1.3841</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="U7" t="n">
         <v>0.1265</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. NOGUER SANTAELLA</t>
+          <t>M. VANCEA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.7574</v>
+        <v>-4.0206</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3784</v>
+        <v>-1.5205</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.379</v>
+        <v>-2.5001</v>
       </c>
       <c r="G8" t="n">
-        <v>-6.0902</v>
+        <v>-0.8589</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.2464</v>
+        <v>0.2203</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.8438</v>
+        <v>-1.0792</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.2894</v>
+        <v>0.6344</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.1435</v>
+        <v>0.6344</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.1459</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.8008</v>
+        <v>-1.4933</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1028</v>
+        <v>-0.4142</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.698</v>
+        <v>-1.0792</v>
       </c>
       <c r="P8" t="n">
-        <v>1.9534</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9534</v>
+        <v>0.3907</v>
       </c>
       <c r="S8" t="n">
-        <v>1.598</v>
+        <v>-0.3804</v>
       </c>
       <c r="T8" t="n">
-        <v>1.3565</v>
+        <v>-0.2015</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2415</v>
+        <v>-0.1789</v>
       </c>
       <c r="V8" t="n">
         <v>-1.2186</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.7731</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. VANCEA</t>
+          <t>R. NOGUER SANTAELLA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.1762</v>
+        <v>-4.757</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6216</v>
+        <v>-1.1873</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.5546</v>
+        <v>-3.5697</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8589</v>
+        <v>-6.0902</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2203</v>
+        <v>-2.2464</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.0792</v>
+        <v>-3.8438</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6344</v>
+        <v>-2.2894</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6344</v>
+        <v>-1.1435</v>
       </c>
       <c r="L9" t="n">
+        <v>-1.1459</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-3.8008</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-1.1028</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-2.698</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.9534</v>
+      </c>
+      <c r="Q9" t="n">
         <v>0</v>
       </c>
-      <c r="M9" t="n">
-        <v>-1.4933</v>
-      </c>
-      <c r="N9" t="n">
-        <v>-0.4142</v>
-      </c>
-      <c r="O9" t="n">
-        <v>-1.0792</v>
-      </c>
-      <c r="P9" t="n">
-        <v>-1.5627</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>-1.9534</v>
-      </c>
       <c r="R9" t="n">
-        <v>0.3907</v>
+        <v>1.9534</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5359</v>
+        <v>0.5984</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3026</v>
+        <v>0.5476</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2333</v>
+        <v>0.0508</v>
       </c>
       <c r="V9" t="n">
         <v>-1.2186</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2186</v>
+        <v>-1.7731</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-7.1498</v>
+        <v>-6.4687</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.5598</v>
+        <v>-2.9332</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.5901</v>
+        <v>-3.5356</v>
       </c>
       <c r="G10" t="n">
         <v>-7.09</v>
@@ -1234,13 +1234,13 @@
         <v>2.3441</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1082</v>
+        <v>-0.4271</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8941</v>
+        <v>-0.2674</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2141</v>
+        <v>-0.1597</v>
       </c>
       <c r="V10" t="n">
         <v>0.853</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.8296</v>
+        <v>-6.9389</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.2139</v>
+        <v>-4.405</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.6156</v>
+        <v>-2.5339</v>
       </c>
       <c r="G11" t="n">
         <v>-3.3583</v>
@@ -1312,13 +1312,13 @@
         <v>1.1721</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5178</v>
+        <v>0.3728</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4704</v>
+        <v>0.3385</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0474</v>
+        <v>0.0343</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2186</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-28.204</v>
+        <v>-27.5986</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.0115</v>
+        <v>-4.4063</v>
       </c>
       <c r="F12" t="n">
-        <v>-23.1925</v>
+        <v>-23.1924</v>
       </c>
       <c r="G12" t="n">
         <v>-20.5528</v>
@@ -1366,10 +1366,10 @@
         <v>7.989599999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>7.982800000000002</v>
+        <v>7.9828</v>
       </c>
       <c r="L12" t="n">
-        <v>0.006800000000000139</v>
+        <v>0.006799999999999695</v>
       </c>
       <c r="M12" t="n">
         <v>-28.5426</v>
@@ -1390,13 +1390,13 @@
         <v>17.5809</v>
       </c>
       <c r="S12" t="n">
-        <v>3.2746</v>
+        <v>3.8796</v>
       </c>
       <c r="T12" t="n">
-        <v>3.1514</v>
+        <v>3.756600000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1232</v>
+        <v>0.1231</v>
       </c>
       <c r="V12" t="n">
         <v>-8.972200000000001</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>N. CLEDJO HOUNGUES</t>
+          <t>S. MENENDEZ PEREZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.2614</v>
+        <v>8.9415</v>
       </c>
       <c r="E13" t="n">
-        <v>7.0204</v>
+        <v>6.4894</v>
       </c>
       <c r="F13" t="n">
-        <v>2.241</v>
+        <v>2.4521</v>
       </c>
       <c r="G13" t="n">
-        <v>6.9499</v>
+        <v>6.4628</v>
       </c>
       <c r="H13" t="n">
-        <v>4.7926</v>
+        <v>1.0412</v>
       </c>
       <c r="I13" t="n">
-        <v>2.1573</v>
+        <v>5.4216</v>
       </c>
       <c r="J13" t="n">
-        <v>8.8725</v>
+        <v>6.8926</v>
       </c>
       <c r="K13" t="n">
-        <v>6.0399</v>
+        <v>1.7396</v>
       </c>
       <c r="L13" t="n">
-        <v>2.8326</v>
+        <v>5.153</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.9226</v>
+        <v>-0.4297</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.2474</v>
+        <v>-0.6984</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.6753</v>
+        <v>0.2687</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.9301</v>
+        <v>1.5627</v>
       </c>
       <c r="Q13" t="n">
-        <v>-6.251</v>
+        <v>-1.1721</v>
       </c>
       <c r="R13" t="n">
-        <v>3.3208</v>
+        <v>2.7348</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9216</v>
+        <v>-0.3027</v>
       </c>
       <c r="T13" t="n">
-        <v>0.743</v>
+        <v>-0.4497</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1786</v>
+        <v>0.147</v>
       </c>
       <c r="V13" t="n">
-        <v>4.3201</v>
+        <v>1.2186</v>
       </c>
       <c r="W13" t="n">
-        <v>3.6559</v>
+        <v>1.2186</v>
       </c>
       <c r="X13" t="n">
-        <v>0.6642</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S. MENENDEZ PEREZ</t>
+          <t>N. CLEDJO HOUNGUES</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.714700000000001</v>
+        <v>8.483499999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>6.2872</v>
+        <v>6.5149</v>
       </c>
       <c r="F14" t="n">
-        <v>2.4276</v>
+        <v>1.9686</v>
       </c>
       <c r="G14" t="n">
-        <v>6.4628</v>
+        <v>6.9499</v>
       </c>
       <c r="H14" t="n">
-        <v>1.0412</v>
+        <v>4.7926</v>
       </c>
       <c r="I14" t="n">
-        <v>5.4216</v>
+        <v>2.1573</v>
       </c>
       <c r="J14" t="n">
-        <v>6.8926</v>
+        <v>8.8725</v>
       </c>
       <c r="K14" t="n">
-        <v>1.7396</v>
+        <v>6.0399</v>
       </c>
       <c r="L14" t="n">
-        <v>5.153</v>
+        <v>2.8326</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.4297</v>
+        <v>-1.9226</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.6984</v>
+        <v>-1.2474</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2687</v>
+        <v>-0.6753</v>
       </c>
       <c r="P14" t="n">
-        <v>1.5627</v>
+        <v>-2.9301</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1721</v>
+        <v>-6.251</v>
       </c>
       <c r="R14" t="n">
-        <v>2.7348</v>
+        <v>3.3208</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5295</v>
+        <v>0.1437</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.652</v>
+        <v>0.2374</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1225</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2186</v>
+        <v>4.3201</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2186</v>
+        <v>3.6559</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>0.6642</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.6046</v>
+        <v>5.8715</v>
       </c>
       <c r="E15" t="n">
-        <v>5.2565</v>
+        <v>5.661</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3481</v>
+        <v>0.2105</v>
       </c>
       <c r="G15" t="n">
         <v>5.5271</v>
@@ -1624,13 +1624,13 @@
         <v>3.1255</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8173</v>
+        <v>-0.5503</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.652</v>
+        <v>-0.2475</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1653</v>
+        <v>-0.3028</v>
       </c>
       <c r="V15" t="n">
         <v>-0.2772</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.5064</v>
+        <v>3.2104</v>
       </c>
       <c r="E16" t="n">
-        <v>2.247</v>
+        <v>2.6514</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2594</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="G16" t="n">
         <v>0.5272</v>
@@ -1702,13 +1702,13 @@
         <v>2.9301</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.2282</v>
+        <v>-0.5241</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4704</v>
+        <v>-0.0659</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7578</v>
+        <v>-0.4582</v>
       </c>
       <c r="V16" t="n">
         <v>0.2772</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.0484</v>
+        <v>2.5346</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8623</v>
+        <v>2.2668</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1861</v>
+        <v>0.2678</v>
       </c>
       <c r="G17" t="n">
         <v>1.8243</v>
@@ -1780,13 +1780,13 @@
         <v>1.9534</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8893</v>
+        <v>-0.4031</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3026</v>
+        <v>0.1018</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5867</v>
+        <v>-0.5049</v>
       </c>
       <c r="V17" t="n">
         <v>0.3321</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.6065</v>
+        <v>2.1887</v>
       </c>
       <c r="E18" t="n">
-        <v>2.8513</v>
+        <v>3.0535</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2448</v>
+        <v>-0.8649</v>
       </c>
       <c r="G18" t="n">
         <v>1.2522</v>
@@ -1858,13 +1858,13 @@
         <v>0.7814</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8875999999999999</v>
+        <v>-0.3054</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2421</v>
+        <v>-0.0399</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6455</v>
+        <v>-0.2656</v>
       </c>
       <c r="V18" t="n">
         <v>1.8279</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>F. ALEN GARCIA</t>
+          <t>D. CAJAL PENACHO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6428</v>
+        <v>0.7029</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3375</v>
+        <v>-0.5339</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3052</v>
+        <v>1.2368</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5304</v>
+        <v>0.2724</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.8401</v>
+        <v>-0.5093</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3097</v>
+        <v>0.7817</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.3855</v>
+        <v>0.9669</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.426</v>
+        <v>0.1842</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0405</v>
+        <v>0.7827</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1449</v>
+        <v>-0.6945</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4142</v>
+        <v>-0.6935</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2692</v>
+        <v>-0.001</v>
       </c>
       <c r="P19" t="n">
-        <v>0.586</v>
+        <v>0.7814</v>
       </c>
       <c r="Q19" t="n">
+        <v>-1.1721</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.9534</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-0.3508</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-0.3287</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-0.0221</v>
+      </c>
+      <c r="V19" t="n">
         <v>0</v>
       </c>
-      <c r="R19" t="n">
-        <v>0.586</v>
-      </c>
-      <c r="S19" t="n">
-        <v>-0.077</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0.4458</v>
-      </c>
-      <c r="U19" t="n">
-        <v>-0.5228</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0.6642</v>
-      </c>
       <c r="W19" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.3869</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. CAJAL PENACHO</t>
+          <t>F. ALEN GARCIA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0131</v>
+        <v>0.6441</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7361</v>
+        <v>-0.067</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7493</v>
+        <v>0.7111</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2724</v>
+        <v>-0.5304</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5093</v>
+        <v>-0.8401</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7817</v>
+        <v>0.3097</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9669</v>
+        <v>-0.3855</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1842</v>
+        <v>-0.426</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7827</v>
+        <v>0.0405</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6945</v>
+        <v>-0.1449</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6935</v>
+        <v>-0.4142</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.001</v>
+        <v>0.2692</v>
       </c>
       <c r="P20" t="n">
-        <v>0.7814</v>
+        <v>0.586</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.9534</v>
+        <v>0.586</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0406</v>
+        <v>-0.0757</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5309</v>
+        <v>0.0413</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5096000000000001</v>
+        <v>-0.117</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.6642</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.3869</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>F. GASPAR AGUILAR</t>
+          <t>O. LOPEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5164</v>
+        <v>-1.3872</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.9364</v>
+        <v>0.1038</v>
       </c>
       <c r="F21" t="n">
-        <v>1.42</v>
+        <v>-1.491</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.2511</v>
+        <v>-0.4814</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.9923</v>
+        <v>-1.1016</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7412</v>
+        <v>0.6202</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6125</v>
+        <v>1.3563</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.8148</v>
+        <v>0.0614</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2023</v>
+        <v>1.2949</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.6385999999999999</v>
+        <v>-1.8377</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.1775</v>
+        <v>-1.163</v>
       </c>
       <c r="O21" t="n">
-        <v>0.5389</v>
+        <v>-0.6747</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.5627</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.3208</v>
+        <v>-1.1721</v>
       </c>
       <c r="R21" t="n">
-        <v>1.7581</v>
+        <v>0.3907</v>
       </c>
       <c r="S21" t="n">
-        <v>1.6882</v>
+        <v>-0.1245</v>
       </c>
       <c r="T21" t="n">
-        <v>1.7197</v>
+        <v>-0.0805</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0315</v>
+        <v>-0.044</v>
       </c>
       <c r="V21" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.3321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>O. LOPEZ SANCHEZ</t>
+          <t>F. GASPAR AGUILAR</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.6776</v>
+        <v>-1.6378</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0027</v>
+        <v>-2.9475</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.6803</v>
+        <v>1.3097</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.4814</v>
+        <v>-1.2511</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.1016</v>
+        <v>-1.9923</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6202</v>
+        <v>0.7412</v>
       </c>
       <c r="J22" t="n">
-        <v>1.3563</v>
+        <v>-0.6125</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0614</v>
+        <v>-0.8148</v>
       </c>
       <c r="L22" t="n">
-        <v>1.2949</v>
+        <v>0.2023</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.8377</v>
+        <v>-0.6385999999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.163</v>
+        <v>-1.1775</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6747</v>
+        <v>0.5389</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.7814</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1721</v>
+        <v>-3.3208</v>
       </c>
       <c r="R22" t="n">
-        <v>0.3907</v>
+        <v>1.7581</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4149</v>
+        <v>0.5667</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1816</v>
+        <v>0.7085</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2333</v>
+        <v>-0.1418</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.6093</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>0.3321</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>28.2039</v>
+        <v>29.5522</v>
       </c>
       <c r="E23" t="n">
         <v>23.1924</v>
       </c>
       <c r="F23" t="n">
-        <v>5.0116</v>
+        <v>6.359699999999999</v>
       </c>
       <c r="G23" t="n">
         <v>20.553</v>
@@ -2248,13 +2248,13 @@
         <v>19.5342</v>
       </c>
       <c r="S23" t="n">
-        <v>-3.2746</v>
+        <v>-1.9262</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1231</v>
+        <v>-0.1232000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>-3.151399999999999</v>
+        <v>-1.8031</v>
       </c>
       <c r="V23" t="n">
         <v>8.972199999999999</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484270_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484270_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:Y23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.3656</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484270_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.3656</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484270_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.4959</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484270_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-2.4708</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484270_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.5842</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484270_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.4959</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484270_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484270_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.7731</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484270_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.3656</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484270_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484270_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-12.3539</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>0</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484270_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0.6642</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484270_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-2.3824</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484270_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484270_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,11 +1873,16 @@
       <c r="X17" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484270_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. PACÍFICO CANTARELLI</t>
+          <t>M. PACIFICO CANTARELLI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1874,6 +1955,11 @@
       </c>
       <c r="X18" t="n">
         <v>-0.8865</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484270_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484270_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0.3869</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484270_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484270_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0.3321</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484270_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,7 @@
       <c r="X23" t="n">
         <v>-3.3815</v>
       </c>
+      <c r="Y23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
